--- a/data/trans_orig/P05A02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05A02-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>194858</t>
+          <t>195207</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>222748</t>
+          <t>223290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>189453</t>
+          <t>189784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216423</t>
+          <t>215602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>395207</t>
+          <t>391744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>431933</t>
+          <t>430835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44321</t>
+          <t>43570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70849</t>
+          <t>71087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64899</t>
+          <t>65406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90712</t>
+          <t>90883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126472</t>
+          <t>128561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>337164</t>
+          <t>337542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377513</t>
+          <t>376955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329172</t>
+          <t>328313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369116</t>
+          <t>370490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674033</t>
+          <t>676635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736562</t>
+          <t>733309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105082</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>144850</t>
+          <t>144979</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112625</t>
+          <t>112243</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>151664</t>
+          <t>152322</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>228298</t>
+          <t>229364</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>290212</t>
+          <t>283960</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32314</t>
+          <t>33926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44049</t>
+          <t>44161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>241784</t>
+          <t>242772</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>271513</t>
+          <t>270972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212139</t>
+          <t>211124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>245472</t>
+          <t>243486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>462870</t>
+          <t>461911</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>507428</t>
+          <t>507407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38330</t>
+          <t>38462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65443</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55669</t>
+          <t>56793</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85932</t>
+          <t>84688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101756</t>
+          <t>101279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141924</t>
+          <t>139445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27118</t>
+          <t>27141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49350</t>
+          <t>49511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35754</t>
+          <t>35356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61641</t>
+          <t>61459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>270707</t>
+          <t>270539</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>301021</t>
+          <t>300252</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287827</t>
+          <t>288021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>316472</t>
+          <t>316747</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>565350</t>
+          <t>567901</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>608560</t>
+          <t>608978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>46048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74563</t>
+          <t>74619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68834</t>
+          <t>68058</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96613</t>
+          <t>95742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136437</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20883</t>
+          <t>20262</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>22313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>37957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156757</t>
+          <t>154444</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178063</t>
+          <t>177681</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162145</t>
+          <t>162524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182703</t>
+          <t>183877</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>325613</t>
+          <t>325867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>355648</t>
+          <t>354635</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39001</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>37842</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>44972</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>72465</t>
+          <t>72288</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>199200</t>
+          <t>200311</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>226676</t>
+          <t>226773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>189923</t>
+          <t>188993</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>218663</t>
+          <t>218262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>398279</t>
+          <t>398935</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>437676</t>
+          <t>438182</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,96%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38352</t>
+          <t>36808</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63093</t>
+          <t>62021</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47587</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75616</t>
+          <t>75495</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>90462</t>
+          <t>90780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>129348</t>
+          <t>129258</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30461</t>
+          <t>30795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>462539</t>
+          <t>464179</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>502334</t>
+          <t>505512</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>433145</t>
+          <t>433448</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>478559</t>
+          <t>478491</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>907203</t>
+          <t>910867</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>971054</t>
+          <t>970489</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>85858</t>
+          <t>84378</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121730</t>
+          <t>121870</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87428</t>
+          <t>87385</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>123577</t>
+          <t>125362</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>181118</t>
+          <t>183035</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>236735</t>
+          <t>234778</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>17296</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37810</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>60525</t>
+          <t>62288</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94419</t>
+          <t>93776</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>85759</t>
+          <t>85580</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>124640</t>
+          <t>123563</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>558416</t>
+          <t>556757</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>601701</t>
+          <t>599860</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>562548</t>
+          <t>564018</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>612419</t>
+          <t>612780</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1137140</t>
+          <t>1134892</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1202807</t>
+          <t>1201657</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>123069</t>
+          <t>122505</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>162975</t>
+          <t>164900</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>153263</t>
+          <t>152984</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>200635</t>
+          <t>199952</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>288511</t>
+          <t>287031</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>349692</t>
+          <t>351489</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>29213</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>49376</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2514451</t>
+          <t>2509516</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2606516</t>
+          <t>2606784</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2456402</t>
+          <t>2455923</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2556986</t>
+          <t>2556397</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4996877</t>
+          <t>4998598</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5135074</t>
+          <t>5138122</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>569288</t>
+          <t>568350</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>655375</t>
+          <t>659665</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>632750</t>
+          <t>632594</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>720408</t>
+          <t>724066</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1225227</t>
+          <t>1228724</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1355834</t>
+          <t>1357246</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>78417</t>
+          <t>77386</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>114871</t>
+          <t>115947</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>165081</t>
+          <t>164089</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>217956</t>
+          <t>216051</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>253691</t>
+          <t>253328</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>320738</t>
+          <t>316534</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>216246</t>
+          <t>215228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>245768</t>
+          <t>244777</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188091</t>
+          <t>188670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>219079</t>
+          <t>218368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>412816</t>
+          <t>411173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>454888</t>
+          <t>454252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59998</t>
+          <t>59670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43211</t>
+          <t>46404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71702</t>
+          <t>72241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85395</t>
+          <t>85028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123845</t>
+          <t>125802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25197</t>
+          <t>24769</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12253</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30761</t>
+          <t>30824</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24063</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372235</t>
+          <t>371118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411310</t>
+          <t>411128</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392116</t>
+          <t>389939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429890</t>
+          <t>429627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>775809</t>
+          <t>776718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>831088</t>
+          <t>829888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78546</t>
+          <t>79075</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116486</t>
+          <t>116378</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65343</t>
+          <t>67379</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100236</t>
+          <t>101406</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>155194</t>
+          <t>155359</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>205409</t>
+          <t>205856</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>35789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26303</t>
+          <t>28296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53540</t>
+          <t>55055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>297031</t>
+          <t>296495</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>312410</t>
+          <t>312237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>308731</t>
+          <t>308734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>327509</t>
+          <t>328183</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>612667</t>
+          <t>611359</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>637019</t>
+          <t>636643</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>32286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>23906</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47557</t>
+          <t>48184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>297727</t>
+          <t>296675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>325728</t>
+          <t>326749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>270574</t>
+          <t>271339</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>306688</t>
+          <t>306231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>575935</t>
+          <t>577116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>623895</t>
+          <t>622144</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38685</t>
+          <t>37177</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64951</t>
+          <t>66123</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56744</t>
+          <t>56643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89670</t>
+          <t>87074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100007</t>
+          <t>103563</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143943</t>
+          <t>144294</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17896</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39256</t>
+          <t>40239</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>25835</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52286</t>
+          <t>51369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174576</t>
+          <t>173342</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194209</t>
+          <t>194355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159320</t>
+          <t>159207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184389</t>
+          <t>183583</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>340557</t>
+          <t>340222</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>372196</t>
+          <t>373990</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28421</t>
+          <t>30776</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>24614</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47029</t>
+          <t>46947</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41870</t>
+          <t>39584</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71106</t>
+          <t>69734</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19768</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>31604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>244529</t>
+          <t>243721</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>262574</t>
+          <t>261771</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>258877</t>
+          <t>260690</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>273970</t>
+          <t>273980</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>510940</t>
+          <t>511685</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>533602</t>
+          <t>534418</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>15646</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37222</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>11321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>591248</t>
+          <t>588789</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>621286</t>
+          <t>619761</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>620964</t>
+          <t>619579</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>651029</t>
+          <t>650613</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1217998</t>
+          <t>1217621</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1262089</t>
+          <t>1263570</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32741</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>60738</t>
+          <t>60551</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>29643</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55334</t>
+          <t>54338</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70177</t>
+          <t>68268</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>108476</t>
+          <t>106108</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>26378</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>580919</t>
+          <t>583613</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>627893</t>
+          <t>631878</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>624835</t>
+          <t>625386</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>676547</t>
+          <t>674760</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1226008</t>
+          <t>1223955</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1294019</t>
+          <t>1292351</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>129902</t>
+          <t>126335</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>175076</t>
+          <t>173965</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>126911</t>
+          <t>127041</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>173101</t>
+          <t>173247</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>265061</t>
+          <t>269125</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>328256</t>
+          <t>332376</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14378</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32919</t>
+          <t>33267</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>60085</t>
+          <t>58406</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2849446</t>
+          <t>2846352</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2938008</t>
+          <t>2933474</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2908589</t>
+          <t>2906474</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3000181</t>
+          <t>2997835</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5792135</t>
+          <t>5788594</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5915748</t>
+          <t>5912702</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>393689</t>
+          <t>397776</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>477121</t>
+          <t>475595</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>430946</t>
+          <t>429179</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>515749</t>
+          <t>511808</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>846267</t>
+          <t>846882</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>961138</t>
+          <t>959629</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>68873</t>
+          <t>67542</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>104847</t>
+          <t>104909</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>100577</t>
+          <t>101019</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>147296</t>
+          <t>148553</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>180840</t>
+          <t>183156</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>240698</t>
+          <t>242839</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>199977</t>
+          <t>198933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231573</t>
+          <t>230240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>185063</t>
+          <t>185381</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217666</t>
+          <t>216131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>395617</t>
+          <t>397518</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>439445</t>
+          <t>440163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>43361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71200</t>
+          <t>70549</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53714</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84486</t>
+          <t>83164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105884</t>
+          <t>103592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146351</t>
+          <t>143398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29343</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,49 +9654,49 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>17160</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9935</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>28939</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
           <t>10,06%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17160</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10323</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>27799</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>31</t>
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25174</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51797</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>378250</t>
+          <t>378069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414528</t>
+          <t>416635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394778</t>
+          <t>394996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432660</t>
+          <t>432742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>783861</t>
+          <t>787226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>835785</t>
+          <t>840887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,4%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72697</t>
+          <t>72380</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>107010</t>
+          <t>107772</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66073</t>
+          <t>65645</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100797</t>
+          <t>100246</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>146621</t>
+          <t>145864</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>194755</t>
+          <t>195492</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23959</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>33098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>27880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51275</t>
+          <t>51602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285088</t>
+          <t>285811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>303475</t>
+          <t>302916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>307796</t>
+          <t>307213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>325046</t>
+          <t>324691</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>598996</t>
+          <t>598181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>625240</t>
+          <t>624169</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>32754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25511</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53419</t>
+          <t>53118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -10551,97 +10551,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9129</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>2549</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8674</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>8808</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2549</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>10374</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>277054</t>
+          <t>278731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>308984</t>
+          <t>309964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>284425</t>
+          <t>285961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>320335</t>
+          <t>319683</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>572857</t>
+          <t>575564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>618817</t>
+          <t>620578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35020</t>
+          <t>34974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61724</t>
+          <t>62218</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41662</t>
+          <t>44156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72596</t>
+          <t>73873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86946</t>
+          <t>86121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124633</t>
+          <t>124348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>33025</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36853</t>
+          <t>36988</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64439</t>
+          <t>65328</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192090</t>
+          <t>190902</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205338</t>
+          <t>204523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192081</t>
+          <t>192529</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208144</t>
+          <t>208352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>390390</t>
+          <t>388805</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>410731</t>
+          <t>409615</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15455</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>34927</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>232837</t>
+          <t>231468</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>251189</t>
+          <t>250453</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>239867</t>
+          <t>240653</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>258200</t>
+          <t>258367</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>479527</t>
+          <t>478782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>504548</t>
+          <t>504660</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>29799</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>29113</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28094</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>53980</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>556836</t>
+          <t>557535</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>593348</t>
+          <t>593058</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>563266</t>
+          <t>564778</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>602083</t>
+          <t>601234</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1131994</t>
+          <t>1133280</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1186559</t>
+          <t>1185034</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51042</t>
+          <t>51287</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>84072</t>
+          <t>83337</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>65367</t>
+          <t>64599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>97782</t>
+          <t>97379</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>123641</t>
+          <t>123699</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>171802</t>
+          <t>169246</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>25668</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14527</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35462</t>
+          <t>35213</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>27252</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53425</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>731638</t>
+          <t>731056</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>754261</t>
+          <t>754914</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>755392</t>
+          <t>756559</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>783356</t>
+          <t>784350</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1496412</t>
+          <t>1497279</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1533254</t>
+          <t>1532463</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>18115</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>29184</t>
+          <t>29434</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>54611</t>
+          <t>54849</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>52050</t>
+          <t>51220</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>86083</t>
+          <t>84469</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13058</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>22320</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2928051</t>
+          <t>2930651</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3006962</t>
+          <t>3006579</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3005538</t>
+          <t>3001524</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3088312</t>
+          <t>3085756</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5958420</t>
+          <t>5953218</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6071663</t>
+          <t>6070705</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>300915</t>
+          <t>303176</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>374507</t>
+          <t>374638</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>339054</t>
+          <t>338626</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>414030</t>
+          <t>417635</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>665675</t>
+          <t>661186</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>769525</t>
+          <t>764242</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>63289</t>
+          <t>64735</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>96501</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>85805</t>
+          <t>87817</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>130708</t>
+          <t>132957</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>159478</t>
+          <t>158586</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>215459</t>
+          <t>216227</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>303305</t>
+          <t>303202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>310429</t>
+          <t>310323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>263023</t>
+          <t>263790</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288330</t>
+          <t>288283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>570959</t>
+          <t>572288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>597325</t>
+          <t>597260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26253</t>
+          <t>25173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29456</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -13979,97 +13979,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>332</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1180</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>440364</t>
+          <t>441180</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>474711</t>
+          <t>476597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>433450</t>
+          <t>431259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462070</t>
+          <t>461016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>884271</t>
+          <t>883079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928558</t>
+          <t>927558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40004</t>
+          <t>39755</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74102</t>
+          <t>73668</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45135</t>
+          <t>45684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72434</t>
+          <t>74966</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>94200</t>
+          <t>94907</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>137690</t>
+          <t>137910</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14455,7 +14455,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263458</t>
+          <t>262277</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>288836</t>
+          <t>287359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>300449</t>
+          <t>297720</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>321248</t>
+          <t>320434</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>570962</t>
+          <t>569875</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>603796</t>
+          <t>600828</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35316</t>
+          <t>35499</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18739</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37283</t>
+          <t>37952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>39814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65797</t>
+          <t>67055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>24065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>18233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>268210</t>
+          <t>267522</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>292009</t>
+          <t>291781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>404757</t>
+          <t>404895</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>444047</t>
+          <t>444052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>683558</t>
+          <t>683784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>727312</t>
+          <t>727077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42224</t>
+          <t>41919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27356</t>
+          <t>26915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63218</t>
+          <t>63023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56422</t>
+          <t>54757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95885</t>
+          <t>94880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160859</t>
+          <t>161645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171565</t>
+          <t>172119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230361</t>
+          <t>230127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246944</t>
+          <t>247653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395714</t>
+          <t>394913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>415826</t>
+          <t>415383</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>39841</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234553</t>
+          <t>234441</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>253150</t>
+          <t>251857</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>228042</t>
+          <t>228379</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>242682</t>
+          <t>242696</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>467654</t>
+          <t>468047</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>490481</t>
+          <t>490918</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>28056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23162</t>
+          <t>24055</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>42115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14208</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>520191</t>
+          <t>521226</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>563376</t>
+          <t>564180</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>732508</t>
+          <t>731007</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>808724</t>
+          <t>807793</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1273225</t>
+          <t>1270555</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1370984</t>
+          <t>1366095</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29810</t>
+          <t>28967</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>64265</t>
+          <t>62023</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>67568</t>
+          <t>68603</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>54900</t>
+          <t>56088</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>116601</t>
+          <t>117396</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>23157</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>52055</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15600</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>52444</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>42717</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>92611</t>
+          <t>90938</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>865883</t>
+          <t>863890</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>913513</t>
+          <t>912527</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>651361</t>
+          <t>652264</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>675612</t>
+          <t>675521</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1525574</t>
+          <t>1523472</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1587861</t>
+          <t>1584782</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>52438</t>
+          <t>54735</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>58187</t>
+          <t>57360</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>47674</t>
+          <t>50731</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>103424</t>
+          <t>104153</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24286</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3123610</t>
+          <t>3126460</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3234362</t>
+          <t>3235166</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3331228</t>
+          <t>3323384</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3436876</t>
+          <t>3429221</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6478398</t>
+          <t>6472644</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6622039</t>
+          <t>6617418</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>170623</t>
+          <t>163655</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>257336</t>
+          <t>254831</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>210956</t>
+          <t>214342</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>295674</t>
+          <t>304770</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>418463</t>
+          <t>419031</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>535387</t>
+          <t>538389</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>51369</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>91040</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>59897</t>
+          <t>59914</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>94070</t>
+          <t>96609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>118387</t>
+          <t>121351</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>172434</t>
+          <t>174157</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
